--- a/backend/data/campaign_94_leads.xlsx
+++ b/backend/data/campaign_94_leads.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>Research Month</t>
   </si>
@@ -104,7 +104,7 @@
     <t>https://synchronypharmacy.com/</t>
   </si>
   <si>
-    <t>sakshi.gupta@neutrinotechlabs.com</t>
+    <t>pranav.parvekar@neutrinotechlabs.com</t>
   </si>
   <si>
     <t>Columbus</t>
@@ -117,6 +117,18 @@
   </si>
   <si>
     <t>Pharmaceuticals, Manufacturing</t>
+  </si>
+  <si>
+    <t>bhavana</t>
+  </si>
+  <si>
+    <t>Aakash</t>
+  </si>
+  <si>
+    <t>Shroff</t>
+  </si>
+  <si>
+    <t>aakash.shroff@neutrinotechlabs.com</t>
   </si>
 </sst>
 </file>
@@ -130,7 +142,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="mmm/yy"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +163,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FFBCBEC2"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.5"/>
       <color rgb="FFBCBEC2"/>
       <name val="Arial"/>
@@ -642,137 +661,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -780,6 +799,9 @@
     <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1325,10 +1347,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="2"/>
   <cols>
     <col min="11" max="11" width="26.1818181818182" customWidth="1"/>
+    <col min="17" max="17" width="23.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1431,19 +1454,73 @@
         <v>29</v>
       </c>
     </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K1">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
